--- a/results/reservation_cycle30_20260727.xlsx
+++ b/results/reservation_cycle30_20260727.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -50,8 +50,13 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -59,6 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -94,14 +105,17 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
@@ -434,42 +448,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:O49"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
         <v>Day</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>Block (UTC)</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>Slot # (1-4)</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>Slot start (UTC)</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>Player Name</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>Player ID</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>Alliance</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>Speedup (days)</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>Status</v>
       </c>
-      <c r="J1" s="3" t="str">
-        <v>Preferred blocks (UTC)</v>
+      <c r="K1" s="4" t="str">
+        <v>Player Name</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>Player ID</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>Alliance</v>
+      </c>
+      <c r="N1" s="4" t="str">
+        <v>Speedup (days)</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -478,7 +504,7 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>00:00</v>
       </c>
       <c r="E2" s="2" t="str">
@@ -490,18 +516,30 @@
       <c r="G2" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>2000</v>
       </c>
       <c r="I2" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J2" s="2" t="str">
-        <v/>
+      <c r="K2" s="2" t="str">
+        <v>Ice=아머라카노</v>
+      </c>
+      <c r="L2" s="2">
+        <v>409193945</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>MAR</v>
+      </c>
+      <c r="N2" s="6">
+        <v>160</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B3" s="2" t="str">
@@ -510,7 +548,7 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="5" t="str">
         <v>00:30</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -522,18 +560,30 @@
       <c r="G3" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>200</v>
       </c>
       <c r="I3" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J3" s="2" t="str">
-        <v/>
+      <c r="K3" s="2" t="str">
+        <v>Canada Roach</v>
+      </c>
+      <c r="L3" s="2">
+        <v>408490159</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N3" s="6">
+        <v>140</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -542,7 +592,7 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="5" t="str">
         <v>01:00</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -554,18 +604,30 @@
       <c r="G4" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>180</v>
       </c>
       <c r="I4" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J4" s="2" t="str">
-        <v/>
+      <c r="K4" s="2" t="str">
+        <v>Son Goku</v>
+      </c>
+      <c r="L4" s="2">
+        <v>401977208</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N4" s="6">
+        <v>10</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B5" s="2" t="str">
@@ -574,7 +636,7 @@
       <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>01:30</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -586,18 +648,15 @@
       <c r="G5" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>160</v>
       </c>
       <c r="I5" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -606,7 +665,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>02:00</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -618,18 +677,15 @@
       <c r="G6" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>1000000</v>
       </c>
       <c r="I6" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B7" s="2" t="str">
@@ -638,7 +694,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>02:30</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -650,18 +706,15 @@
       <c r="G7" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>25</v>
       </c>
       <c r="I7" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B8" s="2" t="str">
@@ -670,7 +723,7 @@
       <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="5" t="str">
         <v>03:00</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -682,18 +735,15 @@
       <c r="G8" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>50</v>
       </c>
       <c r="I8" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B9" s="2" t="str">
@@ -702,7 +752,7 @@
       <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="str">
+      <c r="D9" s="5" t="str">
         <v>03:30</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -714,18 +764,15 @@
       <c r="G9" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>84</v>
       </c>
       <c r="I9" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J9" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="str">
+      <c r="A10" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B10" s="2" t="str">
@@ -734,7 +781,7 @@
       <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="5" t="str">
         <v>04:00</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -746,18 +793,15 @@
       <c r="G10" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>547</v>
       </c>
       <c r="I10" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J10" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B11" s="2" t="str">
@@ -766,7 +810,7 @@
       <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="5" t="str">
         <v>04:30</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -778,18 +822,15 @@
       <c r="G11" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="6">
         <v>57</v>
       </c>
       <c r="I11" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J11" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B12" s="2" t="str">
@@ -798,7 +839,7 @@
       <c r="C12" s="2">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="5" t="str">
         <v>05:00</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -810,18 +851,15 @@
       <c r="G12" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>50</v>
       </c>
       <c r="I12" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J12" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B13" s="2" t="str">
@@ -830,7 +868,7 @@
       <c r="C13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="str">
+      <c r="D13" s="5" t="str">
         <v>05:30</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -842,18 +880,15 @@
       <c r="G13" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="6">
         <v>80</v>
       </c>
       <c r="I13" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J13" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B14" s="2" t="str">
@@ -862,7 +897,7 @@
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="5" t="str">
         <v>06:00</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -874,18 +909,15 @@
       <c r="G14" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <v>50</v>
       </c>
       <c r="I14" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J14" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B15" s="2" t="str">
@@ -894,7 +926,7 @@
       <c r="C15" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="str">
+      <c r="D15" s="5" t="str">
         <v>06:30</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -906,18 +938,15 @@
       <c r="G15" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <v>40</v>
       </c>
       <c r="I15" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J15" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B16" s="2" t="str">
@@ -926,7 +955,7 @@
       <c r="C16" s="2">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="5" t="str">
         <v>07:00</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -938,18 +967,15 @@
       <c r="G16" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>62</v>
       </c>
       <c r="I16" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J16" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="str">
+      <c r="A17" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B17" s="2" t="str">
@@ -958,7 +984,7 @@
       <c r="C17" s="2">
         <v>4</v>
       </c>
-      <c r="D17" s="4" t="str">
+      <c r="D17" s="5" t="str">
         <v>07:30</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -970,18 +996,15 @@
       <c r="G17" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>57</v>
       </c>
       <c r="I17" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J17" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="str">
+      <c r="A18" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B18" s="2" t="str">
@@ -990,7 +1013,7 @@
       <c r="C18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="5" t="str">
         <v>08:00</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -1002,18 +1025,15 @@
       <c r="G18" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <v>80</v>
       </c>
       <c r="I18" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J18" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="str">
+      <c r="A19" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B19" s="2" t="str">
@@ -1022,7 +1042,7 @@
       <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="str">
+      <c r="D19" s="5" t="str">
         <v>08:30</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -1034,18 +1054,15 @@
       <c r="G19" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="6">
         <v>50</v>
       </c>
       <c r="I19" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J19" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B20" s="2" t="str">
@@ -1054,7 +1071,7 @@
       <c r="C20" s="2">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="5" t="str">
         <v>09:00</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -1066,18 +1083,15 @@
       <c r="G20" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>103</v>
       </c>
       <c r="I20" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J20" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="str">
+      <c r="A21" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B21" s="2" t="str">
@@ -1086,7 +1100,7 @@
       <c r="C21" s="2">
         <v>4</v>
       </c>
-      <c r="D21" s="4" t="str">
+      <c r="D21" s="5" t="str">
         <v>09:30</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -1098,18 +1112,15 @@
       <c r="G21" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>100</v>
       </c>
       <c r="I21" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J21" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="str">
+      <c r="A22" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B22" s="2" t="str">
@@ -1118,7 +1129,7 @@
       <c r="C22" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="5" t="str">
         <v>10:00</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -1130,18 +1141,15 @@
       <c r="G22" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <v>100</v>
       </c>
       <c r="I22" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J22" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B23" s="2" t="str">
@@ -1150,7 +1158,7 @@
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="str">
+      <c r="D23" s="5" t="str">
         <v>10:30</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -1162,18 +1170,15 @@
       <c r="G23" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>25</v>
       </c>
       <c r="I23" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J23" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="str">
+      <c r="A24" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B24" s="2" t="str">
@@ -1182,7 +1187,7 @@
       <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="5" t="str">
         <v>11:00</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -1194,18 +1199,15 @@
       <c r="G24" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>122</v>
       </c>
       <c r="I24" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J24" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="str">
+      <c r="A25" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B25" s="2" t="str">
@@ -1214,7 +1216,7 @@
       <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="str">
+      <c r="D25" s="5" t="str">
         <v>11:30</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -1226,18 +1228,15 @@
       <c r="G25" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="6">
         <v>40</v>
       </c>
       <c r="I25" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J25" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="str">
+      <c r="A26" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B26" s="2" t="str">
@@ -1246,7 +1245,7 @@
       <c r="C26" s="2">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="5" t="str">
         <v>12:00</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -1258,18 +1257,15 @@
       <c r="G26" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>31</v>
       </c>
       <c r="I26" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J26" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="str">
+      <c r="A27" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B27" s="2" t="str">
@@ -1278,7 +1274,7 @@
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="D27" s="4" t="str">
+      <c r="D27" s="5" t="str">
         <v>12:30</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -1290,18 +1286,15 @@
       <c r="G27" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>63</v>
       </c>
       <c r="I27" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J27" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B28" s="2" t="str">
@@ -1310,7 +1303,7 @@
       <c r="C28" s="2">
         <v>3</v>
       </c>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="5" t="str">
         <v>13:00</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1322,18 +1315,15 @@
       <c r="G28" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J28" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="str">
+      <c r="A29" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B29" s="2" t="str">
@@ -1342,7 +1332,7 @@
       <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="str">
+      <c r="D29" s="5" t="str">
         <v>13:30</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1354,18 +1344,15 @@
       <c r="G29" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>78</v>
       </c>
       <c r="I29" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J29" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="str">
+      <c r="A30" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B30" s="2" t="str">
@@ -1374,7 +1361,7 @@
       <c r="C30" s="2">
         <v>1</v>
       </c>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="5" t="str">
         <v>14:00</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -1386,18 +1373,15 @@
       <c r="G30" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="6">
         <v>88</v>
       </c>
       <c r="I30" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J30" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B31" s="2" t="str">
@@ -1406,7 +1390,7 @@
       <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="str">
+      <c r="D31" s="5" t="str">
         <v>14:30</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -1418,18 +1402,15 @@
       <c r="G31" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>26</v>
       </c>
       <c r="I31" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J31" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="str">
+      <c r="A32" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B32" s="2" t="str">
@@ -1438,7 +1419,7 @@
       <c r="C32" s="2">
         <v>3</v>
       </c>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="5" t="str">
         <v>15:00</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -1450,18 +1431,15 @@
       <c r="G32" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>40</v>
       </c>
       <c r="I32" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J32" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="str">
+      <c r="A33" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B33" s="2" t="str">
@@ -1470,7 +1448,7 @@
       <c r="C33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="str">
+      <c r="D33" s="5" t="str">
         <v>15:30</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -1482,18 +1460,15 @@
       <c r="G33" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>32</v>
       </c>
       <c r="I33" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J33" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="str">
+      <c r="A34" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B34" s="2" t="str">
@@ -1502,7 +1477,7 @@
       <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="5" t="str">
         <v>16:00</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -1514,18 +1489,15 @@
       <c r="G34" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>123</v>
       </c>
       <c r="I34" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J34" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="str">
+      <c r="A35" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B35" s="2" t="str">
@@ -1534,7 +1506,7 @@
       <c r="C35" s="2">
         <v>2</v>
       </c>
-      <c r="D35" s="4" t="str">
+      <c r="D35" s="5" t="str">
         <v>16:30</v>
       </c>
       <c r="E35" s="2" t="str">
@@ -1546,18 +1518,15 @@
       <c r="G35" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>72</v>
       </c>
       <c r="I35" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J35" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="str">
+      <c r="A36" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B36" s="2" t="str">
@@ -1566,7 +1535,7 @@
       <c r="C36" s="2">
         <v>3</v>
       </c>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="5" t="str">
         <v>17:00</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -1578,18 +1547,15 @@
       <c r="G36" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="6">
         <v>60</v>
       </c>
       <c r="I36" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J36" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="str">
+      <c r="A37" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B37" s="2" t="str">
@@ -1598,7 +1564,7 @@
       <c r="C37" s="2">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="str">
+      <c r="D37" s="5" t="str">
         <v>17:30</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -1610,18 +1576,15 @@
       <c r="G37" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="6">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J37" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="str">
+      <c r="A38" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B38" s="2" t="str">
@@ -1630,7 +1593,7 @@
       <c r="C38" s="2">
         <v>1</v>
       </c>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="5" t="str">
         <v>18:00</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -1642,18 +1605,15 @@
       <c r="G38" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="6">
         <v>100</v>
       </c>
       <c r="I38" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J38" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="str">
+      <c r="A39" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B39" s="2" t="str">
@@ -1662,7 +1622,7 @@
       <c r="C39" s="2">
         <v>2</v>
       </c>
-      <c r="D39" s="4" t="str">
+      <c r="D39" s="5" t="str">
         <v>18:30</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -1674,18 +1634,15 @@
       <c r="G39" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="6">
         <v>35</v>
       </c>
       <c r="I39" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J39" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="str">
+      <c r="A40" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B40" s="2" t="str">
@@ -1694,7 +1651,7 @@
       <c r="C40" s="2">
         <v>3</v>
       </c>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="5" t="str">
         <v>19:00</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -1706,18 +1663,15 @@
       <c r="G40" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>29</v>
       </c>
       <c r="I40" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J40" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="str">
+      <c r="A41" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B41" s="2" t="str">
@@ -1726,7 +1680,7 @@
       <c r="C41" s="2">
         <v>4</v>
       </c>
-      <c r="D41" s="4" t="str">
+      <c r="D41" s="5" t="str">
         <v>19:30</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -1738,18 +1692,15 @@
       <c r="G41" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <v>14</v>
       </c>
       <c r="I41" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J41" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="str">
+      <c r="A42" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B42" s="2" t="str">
@@ -1758,7 +1709,7 @@
       <c r="C42" s="2">
         <v>1</v>
       </c>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="5" t="str">
         <v>20:00</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -1770,18 +1721,15 @@
       <c r="G42" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J42" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B43" s="2" t="str">
@@ -1790,7 +1738,7 @@
       <c r="C43" s="2">
         <v>2</v>
       </c>
-      <c r="D43" s="4" t="str">
+      <c r="D43" s="5" t="str">
         <v>20:30</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -1802,18 +1750,15 @@
       <c r="G43" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <v>60</v>
       </c>
       <c r="I43" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J43" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="str">
+      <c r="A44" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B44" s="2" t="str">
@@ -1822,7 +1767,7 @@
       <c r="C44" s="2">
         <v>3</v>
       </c>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="5" t="str">
         <v>21:00</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -1834,18 +1779,15 @@
       <c r="G44" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <v>33</v>
       </c>
       <c r="I44" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J44" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="str">
+      <c r="A45" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B45" s="2" t="str">
@@ -1854,7 +1796,7 @@
       <c r="C45" s="2">
         <v>4</v>
       </c>
-      <c r="D45" s="4" t="str">
+      <c r="D45" s="5" t="str">
         <v>21:30</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -1866,18 +1808,15 @@
       <c r="G45" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J45" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="str">
+      <c r="A46" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B46" s="2" t="str">
@@ -1886,7 +1825,7 @@
       <c r="C46" s="2">
         <v>1</v>
       </c>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="5" t="str">
         <v>22:00</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -1898,18 +1837,15 @@
       <c r="G46" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <v>31</v>
       </c>
       <c r="I46" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J46" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="str">
+      <c r="A47" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B47" s="2" t="str">
@@ -1918,7 +1854,7 @@
       <c r="C47" s="2">
         <v>2</v>
       </c>
-      <c r="D47" s="4" t="str">
+      <c r="D47" s="5" t="str">
         <v>22:30</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -1930,18 +1866,15 @@
       <c r="G47" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="6">
         <v>70</v>
       </c>
       <c r="I47" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J47" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="str">
+      <c r="A48" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B48" s="2" t="str">
@@ -1950,7 +1883,7 @@
       <c r="C48" s="2">
         <v>3</v>
       </c>
-      <c r="D48" s="4" t="str">
+      <c r="D48" s="5" t="str">
         <v>23:00</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -1962,18 +1895,15 @@
       <c r="G48" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="6">
         <v>22</v>
       </c>
       <c r="I48" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J48" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="str">
+      <c r="A49" s="5" t="str">
         <v>mon</v>
       </c>
       <c r="B49" s="2" t="str">
@@ -1982,7 +1912,7 @@
       <c r="C49" s="2">
         <v>4</v>
       </c>
-      <c r="D49" s="4" t="str">
+      <c r="D49" s="5" t="str">
         <v>23:30</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -1994,221 +1924,70 @@
       <c r="G49" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="6">
         <v>20</v>
       </c>
       <c r="I49" s="2" t="str">
         <v>assigned</v>
-      </c>
-      <c r="J49" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="B50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J50" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="str">
-        <v>— Waitlist —</v>
-      </c>
-      <c r="B51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D51" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J51" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="str">
-        <v>mon</v>
-      </c>
-      <c r="B52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v>Ice=아머라카노</v>
-      </c>
-      <c r="F52" s="2">
-        <v>409193945</v>
-      </c>
-      <c r="G52" s="2" t="str">
-        <v>MAR</v>
-      </c>
-      <c r="H52" s="5">
-        <v>160</v>
-      </c>
-      <c r="I52" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J52" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="str">
-        <v>mon</v>
-      </c>
-      <c r="B53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D53" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v>Canada Roach</v>
-      </c>
-      <c r="F53" s="2">
-        <v>408490159</v>
-      </c>
-      <c r="G53" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H53" s="5">
-        <v>140</v>
-      </c>
-      <c r="I53" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J53" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="str">
-        <v>mon</v>
-      </c>
-      <c r="B54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D54" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v>Son Goku</v>
-      </c>
-      <c r="F54" s="2">
-        <v>401977208</v>
-      </c>
-      <c r="G54" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H54" s="5">
-        <v>10</v>
-      </c>
-      <c r="I54" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J54" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:O49"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>Day</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>Block (UTC)</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>Slot # (1-4)</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>Slot start (UTC)</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>Player Name</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>Player ID</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>Alliance</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>Speedup (days)</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>Status</v>
       </c>
-      <c r="J1" s="3" t="str">
-        <v>Preferred blocks (UTC)</v>
+      <c r="K1" s="4" t="str">
+        <v>Player Name</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>Player ID</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>Alliance</v>
+      </c>
+      <c r="N1" s="4" t="str">
+        <v>Speedup (days)</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -2217,7 +1996,7 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>00:00</v>
       </c>
       <c r="E2" s="2" t="str">
@@ -2229,18 +2008,30 @@
       <c r="G2" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>2000</v>
       </c>
       <c r="I2" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J2" s="2" t="str">
-        <v/>
+      <c r="K2" s="2" t="str">
+        <v>Hxnrza</v>
+      </c>
+      <c r="L2" s="2">
+        <v>389117163</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N2" s="6">
+        <v>33</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B3" s="2" t="str">
@@ -2249,7 +2040,7 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="5" t="str">
         <v>00:30</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -2261,18 +2052,30 @@
       <c r="G3" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>120</v>
       </c>
       <c r="I3" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J3" s="2" t="str">
-        <v/>
+      <c r="K3" s="2" t="str">
+        <v>Son Goku</v>
+      </c>
+      <c r="L3" s="2">
+        <v>401977208</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N3" s="6">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -2281,7 +2084,7 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="5" t="str">
         <v>01:00</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -2293,18 +2096,30 @@
       <c r="G4" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>100</v>
       </c>
       <c r="I4" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J4" s="2" t="str">
-        <v/>
+      <c r="K4" s="2" t="str">
+        <v>Ice=아머라카노</v>
+      </c>
+      <c r="L4" s="2">
+        <v>409193945</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <v>MAR</v>
+      </c>
+      <c r="N4" s="6">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B5" s="2" t="str">
@@ -2313,7 +2128,7 @@
       <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>01:30</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -2325,18 +2140,30 @@
       <c r="G5" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>50</v>
       </c>
       <c r="I5" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <v/>
+      <c r="K5" s="2" t="str">
+        <v>Hiro</v>
+      </c>
+      <c r="L5" s="2">
+        <v>399782067</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N5" s="6">
+        <v>11</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -2345,7 +2172,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>02:00</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -2357,18 +2184,15 @@
       <c r="G6" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>110</v>
       </c>
       <c r="I6" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B7" s="2" t="str">
@@ -2377,7 +2201,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>02:30</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -2389,18 +2213,15 @@
       <c r="G7" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>17</v>
       </c>
       <c r="I7" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B8" s="2" t="str">
@@ -2409,7 +2230,7 @@
       <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="5" t="str">
         <v>03:00</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -2421,18 +2242,15 @@
       <c r="G8" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>80</v>
       </c>
       <c r="I8" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B9" s="2" t="str">
@@ -2441,7 +2259,7 @@
       <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="str">
+      <c r="D9" s="5" t="str">
         <v>03:30</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -2453,18 +2271,15 @@
       <c r="G9" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>50</v>
       </c>
       <c r="I9" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J9" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="str">
+      <c r="A10" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B10" s="2" t="str">
@@ -2473,7 +2288,7 @@
       <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="5" t="str">
         <v>04:00</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -2485,18 +2300,15 @@
       <c r="G10" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>477</v>
       </c>
       <c r="I10" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J10" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B11" s="2" t="str">
@@ -2505,7 +2317,7 @@
       <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="5" t="str">
         <v>04:30</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -2517,18 +2329,15 @@
       <c r="G11" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="6">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J11" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B12" s="2" t="str">
@@ -2537,7 +2346,7 @@
       <c r="C12" s="2">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="5" t="str">
         <v>05:00</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -2549,18 +2358,15 @@
       <c r="G12" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>52</v>
       </c>
       <c r="I12" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J12" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B13" s="2" t="str">
@@ -2569,7 +2375,7 @@
       <c r="C13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="str">
+      <c r="D13" s="5" t="str">
         <v>05:30</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -2581,18 +2387,15 @@
       <c r="G13" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="6">
         <v>42</v>
       </c>
       <c r="I13" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J13" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B14" s="2" t="str">
@@ -2601,7 +2404,7 @@
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="5" t="str">
         <v>06:00</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -2613,18 +2416,15 @@
       <c r="G14" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <v>15</v>
       </c>
       <c r="I14" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J14" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B15" s="2" t="str">
@@ -2633,7 +2433,7 @@
       <c r="C15" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="str">
+      <c r="D15" s="5" t="str">
         <v>06:30</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -2645,18 +2445,15 @@
       <c r="G15" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <v>92</v>
       </c>
       <c r="I15" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J15" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B16" s="2" t="str">
@@ -2665,7 +2462,7 @@
       <c r="C16" s="2">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="5" t="str">
         <v>07:00</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -2677,18 +2474,15 @@
       <c r="G16" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>86</v>
       </c>
       <c r="I16" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J16" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="str">
+      <c r="A17" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B17" s="2" t="str">
@@ -2697,7 +2491,7 @@
       <c r="C17" s="2">
         <v>4</v>
       </c>
-      <c r="D17" s="4" t="str">
+      <c r="D17" s="5" t="str">
         <v>07:30</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -2709,18 +2503,15 @@
       <c r="G17" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J17" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="str">
+      <c r="A18" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B18" s="2" t="str">
@@ -2729,7 +2520,7 @@
       <c r="C18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="5" t="str">
         <v>08:00</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -2741,18 +2532,15 @@
       <c r="G18" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <v>65</v>
       </c>
       <c r="I18" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J18" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="str">
+      <c r="A19" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B19" s="2" t="str">
@@ -2761,7 +2549,7 @@
       <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="str">
+      <c r="D19" s="5" t="str">
         <v>08:30</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -2773,18 +2561,15 @@
       <c r="G19" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="6">
         <v>45</v>
       </c>
       <c r="I19" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J19" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B20" s="2" t="str">
@@ -2793,7 +2578,7 @@
       <c r="C20" s="2">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="5" t="str">
         <v>09:00</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -2805,18 +2590,15 @@
       <c r="G20" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>36</v>
       </c>
       <c r="I20" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J20" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="str">
+      <c r="A21" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B21" s="2" t="str">
@@ -2825,7 +2607,7 @@
       <c r="C21" s="2">
         <v>4</v>
       </c>
-      <c r="D21" s="4" t="str">
+      <c r="D21" s="5" t="str">
         <v>09:30</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -2837,18 +2619,15 @@
       <c r="G21" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>44</v>
       </c>
       <c r="I21" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J21" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="str">
+      <c r="A22" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B22" s="2" t="str">
@@ -2857,7 +2636,7 @@
       <c r="C22" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="5" t="str">
         <v>10:00</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -2869,18 +2648,15 @@
       <c r="G22" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <v>104</v>
       </c>
       <c r="I22" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J22" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B23" s="2" t="str">
@@ -2889,7 +2665,7 @@
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="str">
+      <c r="D23" s="5" t="str">
         <v>10:30</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -2901,18 +2677,15 @@
       <c r="G23" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>50</v>
       </c>
       <c r="I23" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J23" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="str">
+      <c r="A24" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B24" s="2" t="str">
@@ -2921,7 +2694,7 @@
       <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="5" t="str">
         <v>11:00</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -2933,18 +2706,15 @@
       <c r="G24" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>105</v>
       </c>
       <c r="I24" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J24" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="str">
+      <c r="A25" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B25" s="2" t="str">
@@ -2953,7 +2723,7 @@
       <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="str">
+      <c r="D25" s="5" t="str">
         <v>11:30</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -2965,18 +2735,15 @@
       <c r="G25" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="6">
         <v>76</v>
       </c>
       <c r="I25" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J25" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="str">
+      <c r="A26" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B26" s="2" t="str">
@@ -2985,7 +2752,7 @@
       <c r="C26" s="2">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="5" t="str">
         <v>12:00</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -2997,18 +2764,15 @@
       <c r="G26" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>73</v>
       </c>
       <c r="I26" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J26" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="str">
+      <c r="A27" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B27" s="2" t="str">
@@ -3017,7 +2781,7 @@
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="D27" s="4" t="str">
+      <c r="D27" s="5" t="str">
         <v>12:30</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -3029,18 +2793,15 @@
       <c r="G27" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>33</v>
       </c>
       <c r="I27" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J27" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B28" s="2" t="str">
@@ -3049,7 +2810,7 @@
       <c r="C28" s="2">
         <v>3</v>
       </c>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="5" t="str">
         <v>13:00</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -3061,18 +2822,15 @@
       <c r="G28" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>32</v>
       </c>
       <c r="I28" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J28" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="str">
+      <c r="A29" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B29" s="2" t="str">
@@ -3081,7 +2839,7 @@
       <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="str">
+      <c r="D29" s="5" t="str">
         <v>13:30</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -3093,18 +2851,15 @@
       <c r="G29" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J29" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="str">
+      <c r="A30" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B30" s="2" t="str">
@@ -3113,7 +2868,7 @@
       <c r="C30" s="2">
         <v>1</v>
       </c>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="5" t="str">
         <v>14:00</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -3125,18 +2880,15 @@
       <c r="G30" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="6">
         <v>11</v>
       </c>
       <c r="I30" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J30" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B31" s="2" t="str">
@@ -3145,7 +2897,7 @@
       <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="str">
+      <c r="D31" s="5" t="str">
         <v>14:30</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -3157,18 +2909,15 @@
       <c r="G31" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>14</v>
       </c>
       <c r="I31" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J31" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="str">
+      <c r="A32" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B32" s="2" t="str">
@@ -3177,7 +2926,7 @@
       <c r="C32" s="2">
         <v>3</v>
       </c>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="5" t="str">
         <v>15:00</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -3189,18 +2938,15 @@
       <c r="G32" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>6</v>
       </c>
       <c r="I32" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J32" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="str">
+      <c r="A33" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B33" s="2" t="str">
@@ -3209,7 +2955,7 @@
       <c r="C33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="str">
+      <c r="D33" s="5" t="str">
         <v>15:30</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -3221,18 +2967,15 @@
       <c r="G33" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J33" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="str">
+      <c r="A34" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B34" s="2" t="str">
@@ -3241,7 +2984,7 @@
       <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="5" t="str">
         <v>16:00</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -3253,18 +2996,15 @@
       <c r="G34" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>65</v>
       </c>
       <c r="I34" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J34" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="str">
+      <c r="A35" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B35" s="2" t="str">
@@ -3273,7 +3013,7 @@
       <c r="C35" s="2">
         <v>2</v>
       </c>
-      <c r="D35" s="4" t="str">
+      <c r="D35" s="5" t="str">
         <v>16:30</v>
       </c>
       <c r="E35" s="2" t="str">
@@ -3285,18 +3025,15 @@
       <c r="G35" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>50</v>
       </c>
       <c r="I35" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J35" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="str">
+      <c r="A36" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B36" s="2" t="str">
@@ -3305,7 +3042,7 @@
       <c r="C36" s="2">
         <v>3</v>
       </c>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="5" t="str">
         <v>17:00</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -3317,18 +3054,15 @@
       <c r="G36" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="6">
         <v>40</v>
       </c>
       <c r="I36" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J36" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="str">
+      <c r="A37" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B37" s="2" t="str">
@@ -3337,7 +3071,7 @@
       <c r="C37" s="2">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="str">
+      <c r="D37" s="5" t="str">
         <v>17:30</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -3349,18 +3083,15 @@
       <c r="G37" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="6">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J37" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="str">
+      <c r="A38" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B38" s="2" t="str">
@@ -3369,7 +3100,7 @@
       <c r="C38" s="2">
         <v>1</v>
       </c>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="5" t="str">
         <v>18:00</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -3381,18 +3112,15 @@
       <c r="G38" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="6">
         <v>134</v>
       </c>
       <c r="I38" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J38" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="str">
+      <c r="A39" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B39" s="2" t="str">
@@ -3401,7 +3129,7 @@
       <c r="C39" s="2">
         <v>2</v>
       </c>
-      <c r="D39" s="4" t="str">
+      <c r="D39" s="5" t="str">
         <v>18:30</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -3413,18 +3141,15 @@
       <c r="G39" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="6">
         <v>60</v>
       </c>
       <c r="I39" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J39" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="str">
+      <c r="A40" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B40" s="2" t="str">
@@ -3433,7 +3158,7 @@
       <c r="C40" s="2">
         <v>3</v>
       </c>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="5" t="str">
         <v>19:00</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -3445,18 +3170,15 @@
       <c r="G40" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>55</v>
       </c>
       <c r="I40" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J40" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="str">
+      <c r="A41" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B41" s="2" t="str">
@@ -3465,7 +3187,7 @@
       <c r="C41" s="2">
         <v>4</v>
       </c>
-      <c r="D41" s="4" t="str">
+      <c r="D41" s="5" t="str">
         <v>19:30</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -3477,18 +3199,15 @@
       <c r="G41" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <v>40</v>
       </c>
       <c r="I41" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J41" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="str">
+      <c r="A42" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B42" s="2" t="str">
@@ -3497,7 +3216,7 @@
       <c r="C42" s="2">
         <v>1</v>
       </c>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="5" t="str">
         <v>20:00</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -3509,18 +3228,15 @@
       <c r="G42" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <v>130</v>
       </c>
       <c r="I42" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J42" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B43" s="2" t="str">
@@ -3529,7 +3245,7 @@
       <c r="C43" s="2">
         <v>2</v>
       </c>
-      <c r="D43" s="4" t="str">
+      <c r="D43" s="5" t="str">
         <v>20:30</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -3541,18 +3257,15 @@
       <c r="G43" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <v>37</v>
       </c>
       <c r="I43" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J43" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="str">
+      <c r="A44" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B44" s="2" t="str">
@@ -3561,7 +3274,7 @@
       <c r="C44" s="2">
         <v>3</v>
       </c>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="5" t="str">
         <v>21:00</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -3573,18 +3286,15 @@
       <c r="G44" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <v>33</v>
       </c>
       <c r="I44" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J44" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="str">
+      <c r="A45" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B45" s="2" t="str">
@@ -3593,7 +3303,7 @@
       <c r="C45" s="2">
         <v>4</v>
       </c>
-      <c r="D45" s="4" t="str">
+      <c r="D45" s="5" t="str">
         <v>21:30</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -3605,18 +3315,15 @@
       <c r="G45" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <v>4</v>
       </c>
       <c r="I45" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J45" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="str">
+      <c r="A46" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B46" s="2" t="str">
@@ -3625,7 +3332,7 @@
       <c r="C46" s="2">
         <v>1</v>
       </c>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="5" t="str">
         <v>22:00</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -3637,18 +3344,15 @@
       <c r="G46" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <v>24</v>
       </c>
       <c r="I46" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J46" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="str">
+      <c r="A47" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B47" s="2" t="str">
@@ -3657,7 +3361,7 @@
       <c r="C47" s="2">
         <v>2</v>
       </c>
-      <c r="D47" s="4" t="str">
+      <c r="D47" s="5" t="str">
         <v>22:30</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -3669,18 +3373,15 @@
       <c r="G47" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="6">
         <v>70</v>
       </c>
       <c r="I47" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J47" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="str">
+      <c r="A48" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B48" s="2" t="str">
@@ -3689,7 +3390,7 @@
       <c r="C48" s="2">
         <v>3</v>
       </c>
-      <c r="D48" s="4" t="str">
+      <c r="D48" s="5" t="str">
         <v>23:00</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -3701,18 +3402,15 @@
       <c r="G48" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="6">
         <v>100</v>
       </c>
       <c r="I48" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J48" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="str">
+      <c r="A49" s="5" t="str">
         <v>tue</v>
       </c>
       <c r="B49" s="2" t="str">
@@ -3721,7 +3419,7 @@
       <c r="C49" s="2">
         <v>4</v>
       </c>
-      <c r="D49" s="4" t="str">
+      <c r="D49" s="5" t="str">
         <v>23:30</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -3733,253 +3431,70 @@
       <c r="G49" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="6">
         <v>35</v>
       </c>
       <c r="I49" s="2" t="str">
         <v>assigned</v>
-      </c>
-      <c r="J49" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="B50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J50" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="str">
-        <v>— Waitlist —</v>
-      </c>
-      <c r="B51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D51" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J51" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="str">
-        <v>tue</v>
-      </c>
-      <c r="B52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v>Hxnrza</v>
-      </c>
-      <c r="F52" s="2">
-        <v>389117163</v>
-      </c>
-      <c r="G52" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H52" s="5">
-        <v>33</v>
-      </c>
-      <c r="I52" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J52" s="2" t="str">
-        <v>18:00~20:00 UTC</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="str">
-        <v>tue</v>
-      </c>
-      <c r="B53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D53" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v>Son Goku</v>
-      </c>
-      <c r="F53" s="2">
-        <v>401977208</v>
-      </c>
-      <c r="G53" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H53" s="5">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J53" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="str">
-        <v>tue</v>
-      </c>
-      <c r="B54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D54" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v>Ice=아머라카노</v>
-      </c>
-      <c r="F54" s="2">
-        <v>409193945</v>
-      </c>
-      <c r="G54" s="2" t="str">
-        <v>MAR</v>
-      </c>
-      <c r="H54" s="5">
-        <v>12</v>
-      </c>
-      <c r="I54" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J54" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="str">
-        <v>tue</v>
-      </c>
-      <c r="B55" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C55" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D55" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v>Hiro</v>
-      </c>
-      <c r="F55" s="2">
-        <v>399782067</v>
-      </c>
-      <c r="G55" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H55" s="5">
-        <v>11</v>
-      </c>
-      <c r="I55" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J55" s="2" t="str">
-        <v>04:00~06:00 UTC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:O49"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>Day</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>Block (UTC)</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>Slot # (1-4)</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>Slot start (UTC)</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>Player Name</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>Player ID</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>Alliance</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>Speedup (days)</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>Status</v>
       </c>
-      <c r="J1" s="3" t="str">
-        <v>Preferred blocks (UTC)</v>
+      <c r="K1" s="4" t="str">
+        <v>Player Name</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>Player ID</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>Alliance</v>
+      </c>
+      <c r="N1" s="4" t="str">
+        <v>Speedup (days)</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -3988,7 +3503,7 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>00:00</v>
       </c>
       <c r="E2" s="2" t="str">
@@ -4000,18 +3515,30 @@
       <c r="G2" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>100</v>
       </c>
       <c r="I2" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J2" s="2" t="str">
-        <v/>
+      <c r="K2" s="2" t="str">
+        <v>Ice=아머라카노</v>
+      </c>
+      <c r="L2" s="2">
+        <v>409193945</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>MAR</v>
+      </c>
+      <c r="N2" s="6">
+        <v>40</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B3" s="2" t="str">
@@ -4020,7 +3547,7 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="5" t="str">
         <v>00:30</v>
       </c>
       <c r="E3" s="2" t="str">
@@ -4032,18 +3559,30 @@
       <c r="G3" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>100</v>
       </c>
       <c r="I3" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J3" s="2" t="str">
-        <v/>
+      <c r="K3" s="2" t="str">
+        <v>Son Goku</v>
+      </c>
+      <c r="L3" s="2">
+        <v>401977208</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N3" s="6">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="str">
+      <c r="A4" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -4052,7 +3591,7 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="5" t="str">
         <v>01:00</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -4064,18 +3603,30 @@
       <c r="G4" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>50</v>
       </c>
       <c r="I4" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J4" s="2" t="str">
-        <v/>
+      <c r="K4" s="2" t="str">
+        <v>S_VISHAL</v>
+      </c>
+      <c r="L4" s="2">
+        <v>408847600</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <v>BOS</v>
+      </c>
+      <c r="N4" s="6">
+        <v>30</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>waitlist</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B5" s="2" t="str">
@@ -4084,7 +3635,7 @@
       <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>01:30</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -4096,18 +3647,15 @@
       <c r="G5" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>40</v>
       </c>
       <c r="I5" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -4116,7 +3664,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>02:00</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -4128,18 +3676,15 @@
       <c r="G6" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>110</v>
       </c>
       <c r="I6" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B7" s="2" t="str">
@@ -4148,7 +3693,7 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>02:30</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -4160,18 +3705,15 @@
       <c r="G7" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>50</v>
       </c>
       <c r="I7" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B8" s="2" t="str">
@@ -4180,7 +3722,7 @@
       <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="5" t="str">
         <v>03:00</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -4192,18 +3734,15 @@
       <c r="G8" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>94</v>
       </c>
       <c r="I8" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B9" s="2" t="str">
@@ -4212,7 +3751,7 @@
       <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="str">
+      <c r="D9" s="5" t="str">
         <v>03:30</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -4224,18 +3763,15 @@
       <c r="G9" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>20</v>
       </c>
       <c r="I9" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J9" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="str">
+      <c r="A10" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B10" s="2" t="str">
@@ -4244,7 +3780,7 @@
       <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="5" t="str">
         <v>04:00</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -4256,18 +3792,15 @@
       <c r="G10" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>1900</v>
       </c>
       <c r="I10" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J10" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="str">
+      <c r="A11" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B11" s="2" t="str">
@@ -4276,7 +3809,7 @@
       <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="5" t="str">
         <v>04:30</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -4288,18 +3821,15 @@
       <c r="G11" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="6">
         <v>11</v>
       </c>
       <c r="I11" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J11" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="str">
+      <c r="A12" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B12" s="2" t="str">
@@ -4308,7 +3838,7 @@
       <c r="C12" s="2">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="5" t="str">
         <v>05:00</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -4320,18 +3850,15 @@
       <c r="G12" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>87</v>
       </c>
       <c r="I12" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J12" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="str">
+      <c r="A13" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B13" s="2" t="str">
@@ -4340,7 +3867,7 @@
       <c r="C13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="str">
+      <c r="D13" s="5" t="str">
         <v>05:30</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -4352,18 +3879,15 @@
       <c r="G13" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="6">
         <v>76</v>
       </c>
       <c r="I13" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J13" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="str">
+      <c r="A14" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B14" s="2" t="str">
@@ -4372,7 +3896,7 @@
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="5" t="str">
         <v>06:00</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -4384,18 +3908,15 @@
       <c r="G14" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J14" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="str">
+      <c r="A15" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B15" s="2" t="str">
@@ -4404,7 +3925,7 @@
       <c r="C15" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="str">
+      <c r="D15" s="5" t="str">
         <v>06:30</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -4416,18 +3937,15 @@
       <c r="G15" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J15" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="str">
+      <c r="A16" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B16" s="2" t="str">
@@ -4436,7 +3954,7 @@
       <c r="C16" s="2">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="5" t="str">
         <v>07:00</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -4448,18 +3966,15 @@
       <c r="G16" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>58</v>
       </c>
       <c r="I16" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J16" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="str">
+      <c r="A17" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B17" s="2" t="str">
@@ -4468,7 +3983,7 @@
       <c r="C17" s="2">
         <v>4</v>
       </c>
-      <c r="D17" s="4" t="str">
+      <c r="D17" s="5" t="str">
         <v>07:30</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -4480,18 +3995,15 @@
       <c r="G17" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>32</v>
       </c>
       <c r="I17" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J17" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="str">
+      <c r="A18" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B18" s="2" t="str">
@@ -4500,7 +4012,7 @@
       <c r="C18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="5" t="str">
         <v>08:00</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -4512,18 +4024,15 @@
       <c r="G18" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <v>27</v>
       </c>
       <c r="I18" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J18" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="str">
+      <c r="A19" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B19" s="2" t="str">
@@ -4532,7 +4041,7 @@
       <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="str">
+      <c r="D19" s="5" t="str">
         <v>08:30</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -4544,18 +4053,15 @@
       <c r="G19" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="6">
         <v>21</v>
       </c>
       <c r="I19" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J19" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B20" s="2" t="str">
@@ -4564,7 +4070,7 @@
       <c r="C20" s="2">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="5" t="str">
         <v>09:00</v>
       </c>
       <c r="E20" s="2" t="str">
@@ -4576,18 +4082,15 @@
       <c r="G20" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>20</v>
       </c>
       <c r="I20" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J20" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="str">
+      <c r="A21" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B21" s="2" t="str">
@@ -4596,7 +4099,7 @@
       <c r="C21" s="2">
         <v>4</v>
       </c>
-      <c r="D21" s="4" t="str">
+      <c r="D21" s="5" t="str">
         <v>09:30</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -4608,18 +4111,15 @@
       <c r="G21" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J21" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="str">
+      <c r="A22" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B22" s="2" t="str">
@@ -4628,7 +4128,7 @@
       <c r="C22" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="5" t="str">
         <v>10:00</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -4640,18 +4140,15 @@
       <c r="G22" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <v>77</v>
       </c>
       <c r="I22" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J22" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="str">
+      <c r="A23" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B23" s="2" t="str">
@@ -4660,7 +4157,7 @@
       <c r="C23" s="2">
         <v>2</v>
       </c>
-      <c r="D23" s="4" t="str">
+      <c r="D23" s="5" t="str">
         <v>10:30</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -4672,18 +4169,15 @@
       <c r="G23" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>60</v>
       </c>
       <c r="I23" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J23" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="str">
+      <c r="A24" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B24" s="2" t="str">
@@ -4692,7 +4186,7 @@
       <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="5" t="str">
         <v>11:00</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -4704,18 +4198,15 @@
       <c r="G24" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>55</v>
       </c>
       <c r="I24" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J24" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="str">
+      <c r="A25" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B25" s="2" t="str">
@@ -4724,7 +4215,7 @@
       <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="4" t="str">
+      <c r="D25" s="5" t="str">
         <v>11:30</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -4736,18 +4227,15 @@
       <c r="G25" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="6">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J25" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="str">
+      <c r="A26" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B26" s="2" t="str">
@@ -4756,7 +4244,7 @@
       <c r="C26" s="2">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="5" t="str">
         <v>12:00</v>
       </c>
       <c r="E26" s="2" t="str">
@@ -4768,18 +4256,15 @@
       <c r="G26" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>200</v>
       </c>
       <c r="I26" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J26" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="str">
+      <c r="A27" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B27" s="2" t="str">
@@ -4788,7 +4273,7 @@
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="D27" s="4" t="str">
+      <c r="D27" s="5" t="str">
         <v>12:30</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -4800,18 +4285,15 @@
       <c r="G27" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>44</v>
       </c>
       <c r="I27" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J27" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="str">
+      <c r="A28" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B28" s="2" t="str">
@@ -4820,7 +4302,7 @@
       <c r="C28" s="2">
         <v>3</v>
       </c>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="5" t="str">
         <v>13:00</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -4832,18 +4314,15 @@
       <c r="G28" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>18</v>
       </c>
       <c r="I28" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J28" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="str">
+      <c r="A29" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B29" s="2" t="str">
@@ -4852,7 +4331,7 @@
       <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="str">
+      <c r="D29" s="5" t="str">
         <v>13:30</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -4864,18 +4343,15 @@
       <c r="G29" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>65</v>
       </c>
       <c r="I29" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J29" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="str">
+      <c r="A30" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B30" s="2" t="str">
@@ -4884,7 +4360,7 @@
       <c r="C30" s="2">
         <v>1</v>
       </c>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="5" t="str">
         <v>14:00</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -4896,18 +4372,15 @@
       <c r="G30" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="6">
         <v>40</v>
       </c>
       <c r="I30" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J30" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="str">
+      <c r="A31" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B31" s="2" t="str">
@@ -4916,7 +4389,7 @@
       <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="str">
+      <c r="D31" s="5" t="str">
         <v>14:30</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -4928,18 +4401,15 @@
       <c r="G31" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>22</v>
       </c>
       <c r="I31" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J31" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="str">
+      <c r="A32" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B32" s="2" t="str">
@@ -4948,7 +4418,7 @@
       <c r="C32" s="2">
         <v>3</v>
       </c>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="5" t="str">
         <v>15:00</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -4960,18 +4430,15 @@
       <c r="G32" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>53</v>
       </c>
       <c r="I32" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J32" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="str">
+      <c r="A33" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B33" s="2" t="str">
@@ -4980,7 +4447,7 @@
       <c r="C33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="str">
+      <c r="D33" s="5" t="str">
         <v>15:30</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -4992,18 +4459,15 @@
       <c r="G33" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>40</v>
       </c>
       <c r="I33" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J33" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="str">
+      <c r="A34" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B34" s="2" t="str">
@@ -5012,7 +4476,7 @@
       <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="5" t="str">
         <v>16:00</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -5024,18 +4488,15 @@
       <c r="G34" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>200</v>
       </c>
       <c r="I34" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J34" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="str">
+      <c r="A35" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B35" s="2" t="str">
@@ -5044,7 +4505,7 @@
       <c r="C35" s="2">
         <v>2</v>
       </c>
-      <c r="D35" s="4" t="str">
+      <c r="D35" s="5" t="str">
         <v>16:30</v>
       </c>
       <c r="E35" s="2" t="str">
@@ -5056,18 +4517,15 @@
       <c r="G35" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>35</v>
       </c>
       <c r="I35" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J35" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="str">
+      <c r="A36" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B36" s="2" t="str">
@@ -5076,7 +4534,7 @@
       <c r="C36" s="2">
         <v>3</v>
       </c>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="5" t="str">
         <v>17:00</v>
       </c>
       <c r="E36" s="2" t="str">
@@ -5088,18 +4546,15 @@
       <c r="G36" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="6">
         <v>74</v>
       </c>
       <c r="I36" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J36" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="str">
+      <c r="A37" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B37" s="2" t="str">
@@ -5108,7 +4563,7 @@
       <c r="C37" s="2">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="str">
+      <c r="D37" s="5" t="str">
         <v>17:30</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -5120,18 +4575,15 @@
       <c r="G37" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="6">
         <v>75</v>
       </c>
       <c r="I37" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J37" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="str">
+      <c r="A38" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B38" s="2" t="str">
@@ -5140,7 +4592,7 @@
       <c r="C38" s="2">
         <v>1</v>
       </c>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="5" t="str">
         <v>18:00</v>
       </c>
       <c r="E38" s="2" t="str">
@@ -5152,18 +4604,15 @@
       <c r="G38" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="6">
         <v>100</v>
       </c>
       <c r="I38" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J38" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="str">
+      <c r="A39" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B39" s="2" t="str">
@@ -5172,7 +4621,7 @@
       <c r="C39" s="2">
         <v>2</v>
       </c>
-      <c r="D39" s="4" t="str">
+      <c r="D39" s="5" t="str">
         <v>18:30</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -5184,18 +4633,15 @@
       <c r="G39" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="6">
         <v>61</v>
       </c>
       <c r="I39" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J39" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="str">
+      <c r="A40" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B40" s="2" t="str">
@@ -5204,7 +4650,7 @@
       <c r="C40" s="2">
         <v>3</v>
       </c>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="5" t="str">
         <v>19:00</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -5216,18 +4662,15 @@
       <c r="G40" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>50</v>
       </c>
       <c r="I40" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J40" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="str">
+      <c r="A41" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B41" s="2" t="str">
@@ -5236,7 +4679,7 @@
       <c r="C41" s="2">
         <v>4</v>
       </c>
-      <c r="D41" s="4" t="str">
+      <c r="D41" s="5" t="str">
         <v>19:30</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -5248,18 +4691,15 @@
       <c r="G41" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <v>35</v>
       </c>
       <c r="I41" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J41" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="str">
+      <c r="A42" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B42" s="2" t="str">
@@ -5268,7 +4708,7 @@
       <c r="C42" s="2">
         <v>1</v>
       </c>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="5" t="str">
         <v>20:00</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -5280,18 +4720,15 @@
       <c r="G42" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <v>86</v>
       </c>
       <c r="I42" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J42" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="str">
+      <c r="A43" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B43" s="2" t="str">
@@ -5300,7 +4737,7 @@
       <c r="C43" s="2">
         <v>2</v>
       </c>
-      <c r="D43" s="4" t="str">
+      <c r="D43" s="5" t="str">
         <v>20:30</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -5312,18 +4749,15 @@
       <c r="G43" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <v>53</v>
       </c>
       <c r="I43" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J43" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="str">
+      <c r="A44" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B44" s="2" t="str">
@@ -5332,7 +4766,7 @@
       <c r="C44" s="2">
         <v>3</v>
       </c>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="5" t="str">
         <v>21:00</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -5344,18 +4778,15 @@
       <c r="G44" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <v>41</v>
       </c>
       <c r="I44" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J44" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="str">
+      <c r="A45" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B45" s="2" t="str">
@@ -5364,7 +4795,7 @@
       <c r="C45" s="2">
         <v>4</v>
       </c>
-      <c r="D45" s="4" t="str">
+      <c r="D45" s="5" t="str">
         <v>21:30</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -5376,18 +4807,15 @@
       <c r="G45" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <v>80</v>
       </c>
       <c r="I45" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J45" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="str">
+      <c r="A46" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B46" s="2" t="str">
@@ -5396,7 +4824,7 @@
       <c r="C46" s="2">
         <v>1</v>
       </c>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="5" t="str">
         <v>22:00</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -5408,18 +4836,15 @@
       <c r="G46" s="2" t="str">
         <v>BOS</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <v>32</v>
       </c>
       <c r="I46" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J46" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="str">
+      <c r="A47" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B47" s="2" t="str">
@@ -5428,7 +4853,7 @@
       <c r="C47" s="2">
         <v>2</v>
       </c>
-      <c r="D47" s="4" t="str">
+      <c r="D47" s="5" t="str">
         <v>22:30</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -5440,18 +4865,15 @@
       <c r="G47" s="2" t="str">
         <v>SXY</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="6">
         <v>24</v>
       </c>
       <c r="I47" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J47" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="str">
+      <c r="A48" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B48" s="2" t="str">
@@ -5460,7 +4882,7 @@
       <c r="C48" s="2">
         <v>3</v>
       </c>
-      <c r="D48" s="4" t="str">
+      <c r="D48" s="5" t="str">
         <v>23:00</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -5472,18 +4894,15 @@
       <c r="G48" s="2" t="str">
         <v>MAR</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="6">
         <v>21</v>
       </c>
       <c r="I48" s="2" t="str">
         <v>assigned</v>
       </c>
-      <c r="J48" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="str">
+      <c r="A49" s="5" t="str">
         <v>thur</v>
       </c>
       <c r="B49" s="2" t="str">
@@ -5492,7 +4911,7 @@
       <c r="C49" s="2">
         <v>4</v>
       </c>
-      <c r="D49" s="4" t="str">
+      <c r="D49" s="5" t="str">
         <v>23:30</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -5504,179 +4923,16 @@
       <c r="G49" s="2" t="str">
         <v>NWO</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="6">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="str">
         <v>assigned</v>
-      </c>
-      <c r="J49" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="B50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D50" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I50" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J50" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="str">
-        <v>— Waitlist —</v>
-      </c>
-      <c r="B51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D51" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I51" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J51" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="str">
-        <v>thur</v>
-      </c>
-      <c r="B52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C52" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D52" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v>Ice=아머라카노</v>
-      </c>
-      <c r="F52" s="2">
-        <v>409193945</v>
-      </c>
-      <c r="G52" s="2" t="str">
-        <v>MAR</v>
-      </c>
-      <c r="H52" s="5">
-        <v>40</v>
-      </c>
-      <c r="I52" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J52" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="str">
-        <v>thur</v>
-      </c>
-      <c r="B53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C53" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D53" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v>Son Goku</v>
-      </c>
-      <c r="F53" s="2">
-        <v>401977208</v>
-      </c>
-      <c r="G53" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H53" s="5">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J53" s="2" t="str">
-        <v>00:00~02:00 UTC</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="str">
-        <v>thur</v>
-      </c>
-      <c r="B54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="C54" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D54" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v>S_VISHAL</v>
-      </c>
-      <c r="F54" s="2">
-        <v>408847600</v>
-      </c>
-      <c r="G54" s="2" t="str">
-        <v>BOS</v>
-      </c>
-      <c r="H54" s="5">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="str">
-        <v>waitlist</v>
-      </c>
-      <c r="J54" s="2" t="str">
-        <v>18:00~20:00 UTC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5686,31 +4942,31 @@
   <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>Alliance</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>mon Players</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>mon Speedup</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>tue Players</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>tue Speedup</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>thur Players</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>thur Speedup</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>Total Players</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>Total Speedup</v>
       </c>
     </row>
